--- a/performance_test_nvidia/report_template.xlsx
+++ b/performance_test_nvidia/report_template.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="40">
   <si>
     <t>模型</t>
   </si>
@@ -126,10 +126,31 @@
     <t>128+128</t>
   </si>
   <si>
-    <t>150(num_prompt=600)</t>
-  </si>
-  <si>
-    <t>200(num_prompt=800)</t>
+    <t>1(num_prompt=1)</t>
+  </si>
+  <si>
+    <t>5(num_prompt=5)</t>
+  </si>
+  <si>
+    <t>10(num_prompt=10)</t>
+  </si>
+  <si>
+    <t>20(num_prompt=20)</t>
+  </si>
+  <si>
+    <t>50(num_prompt=50)</t>
+  </si>
+  <si>
+    <t>100(num_prompt=100)</t>
+  </si>
+  <si>
+    <t>150(num_prompt=150)</t>
+  </si>
+  <si>
+    <t>200(num_prompt=200)</t>
+  </si>
+  <si>
+    <t>300(num_prompt=300)</t>
   </si>
   <si>
     <t>128+1024</t>
@@ -359,7 +380,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -386,6 +407,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF7EDAFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -571,7 +604,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -581,29 +614,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
-        <color rgb="FF1F2329"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF1F2329"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF1F2329"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,9 +676,11 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
-        <color rgb="FF1F2329"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -665,10 +700,32 @@
     <border>
       <left/>
       <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF1F2329"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF1F2329"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF1F2329"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -683,6 +740,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF1F2329"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -706,6 +778,19 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -832,7 +917,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -844,119 +929,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -987,7 +1072,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -996,25 +1084,43 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="3" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1541,7 +1647,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26.6363636363636" customWidth="1"/>
@@ -1635,395 +1741,1529 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
-      <c r="L4" s="17" t="s">
+      <c r="L4" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
     </row>
     <row r="5" ht="15" spans="1:14">
-      <c r="A5" s="5"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="L5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="19" t="s">
+      <c r="M5" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="28" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" ht="15" spans="1:14">
-      <c r="A6" s="5"/>
-      <c r="B6" s="14" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" ht="15" spans="1:14">
-      <c r="A7" s="5"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
     </row>
     <row r="8" ht="15" spans="1:14">
-      <c r="A8" s="5"/>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+    </row>
+    <row r="9" ht="15" spans="1:14">
+      <c r="A9" s="10"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+    </row>
+    <row r="10" ht="15" spans="1:14">
+      <c r="A10" s="10"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+    </row>
+    <row r="11" ht="15" spans="1:14">
+      <c r="A11" s="10"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+    </row>
+    <row r="12" ht="15" spans="1:14">
+      <c r="A12" s="10"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+    </row>
+    <row r="13" ht="15" spans="1:14">
+      <c r="A13" s="10"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+    </row>
+    <row r="14" ht="15" spans="1:14">
+      <c r="A14" s="10"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18"/>
+    </row>
+    <row r="15" ht="15" spans="1:14">
+      <c r="A15" s="10"/>
+      <c r="B15" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" ht="15" spans="1:14">
-      <c r="A9" s="5"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="15" t="s">
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
+    </row>
+    <row r="16" ht="15" spans="1:14">
+      <c r="A16" s="10"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" ht="15" spans="1:14">
-      <c r="A10" s="5"/>
-      <c r="B10" s="14" t="s">
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+    </row>
+    <row r="17" ht="15" spans="1:14">
+      <c r="A17" s="10"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+    </row>
+    <row r="18" ht="15" spans="1:14">
+      <c r="A18" s="10"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="21"/>
+      <c r="N18" s="21"/>
+    </row>
+    <row r="19" ht="15" spans="1:14">
+      <c r="A19" s="10"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+    </row>
+    <row r="20" ht="15" spans="1:14">
+      <c r="A20" s="10"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+    </row>
+    <row r="21" ht="15" spans="1:14">
+      <c r="A21" s="10"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+    </row>
+    <row r="22" ht="15" spans="1:14">
+      <c r="A22" s="10"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+    </row>
+    <row r="23" ht="15" spans="1:14">
+      <c r="A23" s="10"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
+    </row>
+    <row r="24" ht="15" spans="1:14">
+      <c r="A24" s="10"/>
+      <c r="B24" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-    </row>
-    <row r="11" ht="15" spans="1:14">
-      <c r="A11" s="5"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15" t="s">
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
+    </row>
+    <row r="25" ht="15" spans="1:14">
+      <c r="A25" s="10"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" ht="15" spans="1:14">
-      <c r="A12" s="5"/>
-      <c r="B12" s="14" t="s">
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+    </row>
+    <row r="26" ht="15" spans="1:14">
+      <c r="A26" s="10"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+    </row>
+    <row r="27" ht="15" spans="1:14">
+      <c r="A27" s="10"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="21"/>
+      <c r="L27" s="21"/>
+      <c r="M27" s="21"/>
+      <c r="N27" s="21"/>
+    </row>
+    <row r="28" ht="15" spans="1:14">
+      <c r="A28" s="10"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="22"/>
+      <c r="N28" s="22"/>
+    </row>
+    <row r="29" ht="15" spans="1:14">
+      <c r="A29" s="10"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+    </row>
+    <row r="30" ht="15" spans="1:14">
+      <c r="A30" s="10"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+    </row>
+    <row r="31" ht="15" spans="1:14">
+      <c r="A31" s="10"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+    </row>
+    <row r="32" ht="15" spans="1:14">
+      <c r="A32" s="10"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
+    </row>
+    <row r="33" ht="15" spans="1:14">
+      <c r="A33" s="10"/>
+      <c r="B33" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" ht="15" spans="1:14">
-      <c r="A13" s="5"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15" t="s">
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+    </row>
+    <row r="34" ht="15" spans="1:14">
+      <c r="A34" s="10"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" ht="15" spans="1:14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="14" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+    </row>
+    <row r="35" ht="15" spans="1:14">
+      <c r="A35" s="10"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+    </row>
+    <row r="36" ht="15" spans="1:14">
+      <c r="A36" s="10"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="21"/>
+      <c r="N36" s="21"/>
+    </row>
+    <row r="37" ht="15" spans="1:14">
+      <c r="A37" s="10"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+    </row>
+    <row r="38" ht="15" spans="1:14">
+      <c r="A38" s="10"/>
+      <c r="B38" s="16"/>
+      <c r="C38" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+    </row>
+    <row r="39" ht="15" spans="1:14">
+      <c r="A39" s="10"/>
+      <c r="B39" s="16"/>
+      <c r="C39" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="22"/>
+      <c r="N39" s="22"/>
+    </row>
+    <row r="40" ht="15" spans="1:14">
+      <c r="A40" s="10"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="25"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+    </row>
+    <row r="41" ht="15" spans="1:14">
+      <c r="A41" s="10"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18"/>
+      <c r="N41" s="18"/>
+    </row>
+    <row r="42" ht="15" spans="1:14">
+      <c r="A42" s="10"/>
+      <c r="B42" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" ht="15" spans="1:14">
-      <c r="A15" s="5"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="15" t="s">
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+    </row>
+    <row r="43" ht="15" spans="1:14">
+      <c r="A43" s="10"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-    </row>
-    <row r="16" ht="15" spans="1:14">
-      <c r="A16" s="5"/>
-      <c r="B16" s="14" t="s">
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
+      <c r="N43" s="20"/>
+    </row>
+    <row r="44" ht="15" spans="1:14">
+      <c r="A44" s="10"/>
+      <c r="B44" s="16"/>
+      <c r="C44" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+    </row>
+    <row r="45" ht="15" spans="1:14">
+      <c r="A45" s="10"/>
+      <c r="B45" s="16"/>
+      <c r="C45" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="21"/>
+      <c r="H45" s="21"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
+    </row>
+    <row r="46" ht="15" spans="1:14">
+      <c r="A46" s="10"/>
+      <c r="B46" s="16"/>
+      <c r="C46" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+    </row>
+    <row r="47" ht="15" spans="1:14">
+      <c r="A47" s="10"/>
+      <c r="B47" s="16"/>
+      <c r="C47" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
+      <c r="N47" s="24"/>
+    </row>
+    <row r="48" ht="15" spans="1:14">
+      <c r="A48" s="10"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+    </row>
+    <row r="49" ht="15" spans="1:14">
+      <c r="A49" s="10"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="25"/>
+      <c r="K49" s="25"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="25"/>
+    </row>
+    <row r="50" ht="15" spans="1:14">
+      <c r="A50" s="10"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="18"/>
+      <c r="M50" s="18"/>
+      <c r="N50" s="18"/>
+    </row>
+    <row r="51" ht="15" spans="1:14">
+      <c r="A51" s="10"/>
+      <c r="B51" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-    </row>
-    <row r="17" ht="15" spans="1:14">
-      <c r="A17" s="5"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="15" t="s">
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="18"/>
+      <c r="M51" s="18"/>
+      <c r="N51" s="18"/>
+    </row>
+    <row r="52" ht="15" spans="1:14">
+      <c r="A52" s="10"/>
+      <c r="B52" s="16"/>
+      <c r="C52" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-    </row>
-    <row r="18" ht="15" spans="1:14">
-      <c r="A18" s="5"/>
-      <c r="B18" s="14" t="s">
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+    </row>
+    <row r="53" ht="15" spans="1:14">
+      <c r="A53" s="10"/>
+      <c r="B53" s="16"/>
+      <c r="C53" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="18"/>
+      <c r="M53" s="18"/>
+      <c r="N53" s="18"/>
+    </row>
+    <row r="54" ht="15" spans="1:14">
+      <c r="A54" s="10"/>
+      <c r="B54" s="16"/>
+      <c r="C54" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+    </row>
+    <row r="55" ht="15" spans="1:14">
+      <c r="A55" s="10"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+      <c r="N55" s="22"/>
+    </row>
+    <row r="56" ht="15" spans="1:14">
+      <c r="A56" s="10"/>
+      <c r="B56" s="16"/>
+      <c r="C56" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56" s="24"/>
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="24"/>
+      <c r="N56" s="24"/>
+    </row>
+    <row r="57" ht="15" spans="1:14">
+      <c r="A57" s="10"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="22"/>
+      <c r="H57" s="22"/>
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="22"/>
+      <c r="N57" s="22"/>
+    </row>
+    <row r="58" ht="15" spans="1:14">
+      <c r="A58" s="10"/>
+      <c r="B58" s="16"/>
+      <c r="C58" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="25"/>
+    </row>
+    <row r="59" ht="15" spans="1:14">
+      <c r="A59" s="10"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="18"/>
+      <c r="M59" s="18"/>
+      <c r="N59" s="18"/>
+    </row>
+    <row r="60" ht="15" spans="1:14">
+      <c r="A60" s="10"/>
+      <c r="B60" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-    </row>
-    <row r="19" ht="15" spans="1:14">
-      <c r="A19" s="5"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="15" t="s">
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="18"/>
+      <c r="M60" s="18"/>
+      <c r="N60" s="18"/>
+    </row>
+    <row r="61" ht="15" spans="1:14">
+      <c r="A61" s="10"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" ht="15" spans="1:14">
-      <c r="A20" s="5"/>
-      <c r="B20" s="14" t="s">
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+      <c r="F61" s="20"/>
+      <c r="G61" s="20"/>
+      <c r="H61" s="20"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20"/>
+    </row>
+    <row r="62" ht="15" spans="1:14">
+      <c r="A62" s="10"/>
+      <c r="B62" s="16"/>
+      <c r="C62" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+    </row>
+    <row r="63" ht="15" spans="1:14">
+      <c r="A63" s="10"/>
+      <c r="B63" s="16"/>
+      <c r="C63" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21"/>
+      <c r="M63" s="21"/>
+      <c r="N63" s="21"/>
+    </row>
+    <row r="64" ht="15" spans="1:14">
+      <c r="A64" s="10"/>
+      <c r="B64" s="16"/>
+      <c r="C64" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="22"/>
+      <c r="I64" s="22"/>
+      <c r="J64" s="22"/>
+      <c r="K64" s="22"/>
+      <c r="L64" s="22"/>
+      <c r="M64" s="22"/>
+      <c r="N64" s="22"/>
+    </row>
+    <row r="65" ht="15" spans="1:14">
+      <c r="A65" s="10"/>
+      <c r="B65" s="16"/>
+      <c r="C65" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="24"/>
+      <c r="K65" s="24"/>
+      <c r="L65" s="24"/>
+      <c r="M65" s="24"/>
+      <c r="N65" s="24"/>
+    </row>
+    <row r="66" ht="15" spans="1:14">
+      <c r="A66" s="10"/>
+      <c r="B66" s="16"/>
+      <c r="C66" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="22"/>
+      <c r="I66" s="22"/>
+      <c r="J66" s="22"/>
+      <c r="K66" s="22"/>
+      <c r="L66" s="22"/>
+      <c r="M66" s="22"/>
+      <c r="N66" s="22"/>
+    </row>
+    <row r="67" ht="15" spans="1:14">
+      <c r="A67" s="10"/>
+      <c r="B67" s="16"/>
+      <c r="C67" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25"/>
+      <c r="J67" s="25"/>
+      <c r="K67" s="25"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="25"/>
+    </row>
+    <row r="68" ht="15" spans="1:14">
+      <c r="A68" s="10"/>
+      <c r="B68" s="16"/>
+      <c r="C68" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="18"/>
+      <c r="H68" s="18"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="18"/>
+      <c r="L68" s="18"/>
+      <c r="M68" s="18"/>
+      <c r="N68" s="18"/>
+    </row>
+    <row r="69" ht="15" spans="1:14">
+      <c r="A69" s="10"/>
+      <c r="B69" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C69" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" ht="15" spans="1:14">
-      <c r="A21" s="5"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="15" t="s">
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="18"/>
+      <c r="H69" s="18"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="18"/>
+      <c r="L69" s="18"/>
+      <c r="M69" s="18"/>
+      <c r="N69" s="18"/>
+    </row>
+    <row r="70" ht="15" spans="1:14">
+      <c r="A70" s="10"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" ht="15" spans="1:14">
-      <c r="A22" s="5"/>
-      <c r="B22" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20"/>
+    </row>
+    <row r="71" ht="15" spans="1:14">
+      <c r="A71" s="10"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+    </row>
+    <row r="72" ht="15" spans="1:14">
+      <c r="A72" s="10"/>
+      <c r="B72" s="16"/>
+      <c r="C72" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="21"/>
+      <c r="L72" s="21"/>
+      <c r="M72" s="21"/>
+      <c r="N72" s="21"/>
+    </row>
+    <row r="73" ht="15" spans="1:14">
+      <c r="A73" s="10"/>
+      <c r="B73" s="16"/>
+      <c r="C73" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="22"/>
+      <c r="K73" s="22"/>
+      <c r="L73" s="22"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="22"/>
+    </row>
+    <row r="74" ht="15" spans="1:14">
+      <c r="A74" s="10"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
+      <c r="L74" s="24"/>
+      <c r="M74" s="24"/>
+      <c r="N74" s="24"/>
+    </row>
+    <row r="75" ht="15" spans="1:14">
+      <c r="A75" s="10"/>
+      <c r="B75" s="16"/>
+      <c r="C75" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="22"/>
+      <c r="K75" s="22"/>
+      <c r="L75" s="22"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="22"/>
+    </row>
+    <row r="76" ht="15" spans="1:14">
+      <c r="A76" s="10"/>
+      <c r="B76" s="16"/>
+      <c r="C76" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
+      <c r="H76" s="25"/>
+      <c r="I76" s="25"/>
+      <c r="J76" s="25"/>
+      <c r="K76" s="25"/>
+      <c r="L76" s="25"/>
+      <c r="M76" s="25"/>
+      <c r="N76" s="25"/>
+    </row>
+    <row r="77" ht="15" spans="1:14">
+      <c r="A77" s="10"/>
+      <c r="B77" s="16"/>
+      <c r="C77" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+    </row>
+    <row r="78" ht="15" spans="1:14">
+      <c r="A78" s="10"/>
+      <c r="B78" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" ht="15" spans="1:14">
-      <c r="A23" s="5"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15" t="s">
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="18"/>
+      <c r="H78" s="18"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
+      <c r="N78" s="18"/>
+    </row>
+    <row r="79" ht="15" spans="1:14">
+      <c r="A79" s="10"/>
+      <c r="B79" s="16"/>
+      <c r="C79" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="20"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="20"/>
+      <c r="N79" s="20"/>
+    </row>
+    <row r="80" ht="15" spans="1:14">
+      <c r="A80" s="10"/>
+      <c r="B80" s="16"/>
+      <c r="C80" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="18"/>
+      <c r="H80" s="18"/>
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="18"/>
+      <c r="L80" s="18"/>
+      <c r="M80" s="18"/>
+      <c r="N80" s="18"/>
+    </row>
+    <row r="81" ht="15" spans="1:14">
+      <c r="A81" s="10"/>
+      <c r="B81" s="16"/>
+      <c r="C81" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="21"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="21"/>
+      <c r="H81" s="21"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="21"/>
+      <c r="K81" s="21"/>
+      <c r="L81" s="21"/>
+      <c r="M81" s="21"/>
+      <c r="N81" s="21"/>
+    </row>
+    <row r="82" ht="15" spans="1:14">
+      <c r="A82" s="10"/>
+      <c r="B82" s="16"/>
+      <c r="C82" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D82" s="22"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="22"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="22"/>
+      <c r="J82" s="22"/>
+      <c r="K82" s="22"/>
+      <c r="L82" s="22"/>
+      <c r="M82" s="22"/>
+      <c r="N82" s="22"/>
+    </row>
+    <row r="83" ht="15" spans="1:14">
+      <c r="A83" s="10"/>
+      <c r="B83" s="16"/>
+      <c r="C83" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="24"/>
+      <c r="E83" s="24"/>
+      <c r="F83" s="24"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="24"/>
+      <c r="I83" s="24"/>
+      <c r="J83" s="24"/>
+      <c r="K83" s="24"/>
+      <c r="L83" s="24"/>
+      <c r="M83" s="24"/>
+      <c r="N83" s="24"/>
+    </row>
+    <row r="84" ht="15" spans="1:14">
+      <c r="A84" s="10"/>
+      <c r="B84" s="16"/>
+      <c r="C84" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="22"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="22"/>
+      <c r="J84" s="22"/>
+      <c r="K84" s="22"/>
+      <c r="L84" s="22"/>
+      <c r="M84" s="22"/>
+      <c r="N84" s="22"/>
+    </row>
+    <row r="85" ht="15" spans="1:14">
+      <c r="A85" s="10"/>
+      <c r="B85" s="16"/>
+      <c r="C85" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="25"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="25"/>
+      <c r="L85" s="25"/>
+      <c r="M85" s="25"/>
+      <c r="N85" s="25"/>
+    </row>
+    <row r="86" ht="15" spans="1:14">
+      <c r="A86" s="29"/>
+      <c r="B86" s="16"/>
+      <c r="C86" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18"/>
+      <c r="I86" s="18"/>
+      <c r="J86" s="18"/>
+      <c r="K86" s="18"/>
+      <c r="L86" s="18"/>
+      <c r="M86" s="18"/>
+      <c r="N86" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -2031,16 +3271,16 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="L4:N4"/>
-    <mergeCell ref="A4:A23"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="A4:A86"/>
+    <mergeCell ref="B6:B14"/>
+    <mergeCell ref="B15:B23"/>
+    <mergeCell ref="B24:B32"/>
+    <mergeCell ref="B33:B41"/>
+    <mergeCell ref="B42:B50"/>
+    <mergeCell ref="B51:B59"/>
+    <mergeCell ref="B60:B68"/>
+    <mergeCell ref="B69:B77"/>
+    <mergeCell ref="B78:B86"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" display="python3 benchmark_serving.py --model DeepSeek-R1-Distill-Qwen-32B --tokenizer /home/weight/DeepSeek-R1-Distill-Qwen-32B/ --host 0.0.0.0 --port 8000 --endpoint /v1/completions --dataset-name random --request-rate inf --num-prompts xx --max-concurrency xx --random-input-len xx --random-output-len xx --ignore-eos --backend openai&#10;"/>
